--- a/docs/downloads/05/tbl_agri_equip_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_marovoay_ampijoroa.xlsx
@@ -472,12 +472,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -526,12 +520,6 @@
           <t>Filet</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -580,12 +568,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +580,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +592,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +604,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +616,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +628,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,12 +689,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -755,12 +701,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -791,12 +731,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -827,12 +761,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -845,12 +773,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -899,12 +821,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -935,12 +851,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1007,12 +917,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1061,12 +965,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1097,12 +995,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1115,12 +1007,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1133,12 +1019,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1151,12 +1031,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1187,12 +1061,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1222,12 +1090,6 @@
         <is>
           <t>Tracteur</t>
         </is>
-      </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
